--- a/www/download/COUNTRY.LUX.rpO1.xlsx
+++ b/www/download/COUNTRY.LUX.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.729948331892089</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.767200655768488</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.885559175181254</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.898529053504176</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.93826237298063</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.08271974788869</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.11656987032739</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1.0575296608032</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.88401700995807</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.803923167763008</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.803793921900143</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.796431998962022</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.729660741064353</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.6799020733193</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.71694868579003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>3.18933366032101</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>3.08385401550368</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>2.99810113846762</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>2.67858210884494</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>2.54861001545776</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>2.22450563212408</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>2.122649889677</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>2.16390838595466</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>2.62932254354211</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>2.27174767652337</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>2.34876812248288</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>2.2291955780604</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>2.20364142905195</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>2.1126235312356</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>2.05948291318002</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>3.30599270594898</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>3.17612280262701</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>3.08662969578348</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>3.15649651432393</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>3.38974740166151</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>3.37549968887347</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>3.25040098581324</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>3.32160010685773</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>3.69541396048293</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>3.42850417493477</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>3.4956701613679</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>3.38342174345246</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>3.31210029010098</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>3.23100984311538</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>3.29831688784713</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>347.657</t>
+          <t>3.84762863177433</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>356.525</t>
+          <t>3.69937206792448</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>369.458</t>
+          <t>3.60288290614853</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>384.402</t>
+          <t>3.82693294227217</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>405.671</t>
+          <t>4.27795449283698</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>430.518</t>
+          <t>4.49375856035463</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>450.569</t>
+          <t>4.36018689513699</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>464.123</t>
+          <t>4.40737659707515</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>472.77</t>
+          <t>3.25498867090187</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>488.325</t>
+          <t>4.3731081163602</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>502.605</t>
+          <t>4.38094244592787</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>520.128</t>
+          <t>4.19488111199643</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>542.963</t>
+          <t>4.1358050824169</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>608.296</t>
+          <t>4.0713550944451</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>598.729</t>
+          <t>4.31499252988578</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>314.909</t>
+          <t>625164586643.544</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>322.522</t>
+          <t>541635013232.39</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>334.262</t>
+          <t>515117228940.736</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>348.888</t>
+          <t>598390188492.54</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>370.292</t>
+          <t>639556654598.886</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>393.85</t>
+          <t>691501992986.307</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>414.011</t>
+          <t>772715120097.604</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>426.888</t>
+          <t>819927969518.38</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>435.429</t>
+          <t>1003731568940.93</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>451.042</t>
+          <t>997169267257.527</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>465.533</t>
+          <t>936397319473.924</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>483.124</t>
+          <t>850446511659.092</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>505.824</t>
+          <t>738775838016.234</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>530.593</t>
+          <t>653583705834.993</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>535.24</t>
+          <t>601710227480.16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>174761309152.918</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>155936508810.063</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>146894152424.63</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>169893431128.689</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>189617304277.506</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>207516033704.63</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>235630518504.617</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.94</t>
+          <t>255033158873.367</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>14.69</t>
+          <t>298474155175.086</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>286922779265.603</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>275137967731.013</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>253232522627.619</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.94</t>
+          <t>224712901858.634</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>208026796684.229</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>198709346740.265</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>860190071.000804</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>769665932.995062</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.93</t>
+          <t>786367992.389787</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.43</t>
+          <t>867597896.17091</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>941212518.556589</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>1066161745.8532</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>45.58</t>
+          <t>1164666527.58688</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>1107976424.61687</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>1079167710.70052</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>867550135.191634</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>791761027.558413</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>651221350.301361</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>482006586.592373</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>367261555.768002</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>423095662.29256</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>17239.3108033236</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>17016.3512237236</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>15736.5858882031</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>16408.5516894227</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>16799.7083117805</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>16213.644839205</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>17150.2766744441</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>19569.6315299784</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>25011.4812281777</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>29335.515738649</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>26.94</t>
+          <t>31294.6043937728</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>33142.9560948916</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>38304.9369864794</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>46078.3507819642</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>47587.1543247854</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>28105.3258420298</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17.44</t>
+          <t>27350.2580872363</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>17.04</t>
+          <t>25464.7976317536</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>26845.3953995845</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>26745.3015188767</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.22</t>
+          <t>25497.5603942911</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>26941.7952178576</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>29889.4511358578</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.73</t>
+          <t>38445.570045676</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>20.43</t>
+          <t>45906.2358757709</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>48254.8623107309</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>50836.6446026714</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>58892.8346447225</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>69415.7152865741</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.99</t>
+          <t>66533.7167159731</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>3.34948286612085</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>4175.97367807492</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>4262.33057798998</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>4201.89573519058</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>4246.50582703679</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>35.87</t>
+          <t>4606.21276887394</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>4194.69825802974</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>4462.05534599035</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>4764.50443846394</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>40.68</t>
+          <t>5605.69135876413</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>6783.45067121095</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>33.58</t>
+          <t>7486.53790454033</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>7733.91176882276</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>9099.78319780626</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>34.34</t>
+          <t>10311.1196757243</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>9249.29863451588</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.729948331892089</t>
+          <t>883222.104196303</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200655768488</t>
+          <t>766763.471146923</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559175181254</t>
+          <t>701590.635414161</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898529053504176</t>
+          <t>774783.437713691</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.93826237298063</t>
+          <t>819848.819622445</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271974788869</t>
+          <t>849120.774640831</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987032739</t>
+          <t>910484.864273348</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296608032</t>
+          <t>952326.956211229</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.88401700995807</t>
+          <t>1093712.55102633</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923167763008</t>
+          <t>1027292.44276979</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793921900143</t>
+          <t>954677.19545806</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431998962022</t>
+          <t>846365.3831137</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660741064353</t>
+          <t>717245.138393342</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.6799020733193</t>
+          <t>632684.904757387</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868579003</t>
+          <t>598702.460802244</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>155193222238.462</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>146280070063.201</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>121311685618.081</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>146381856384.668</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>197888796558.231</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>207503461650.354</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>203453838453.779</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>199752643788.414</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>267720041703.32</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>259671242560.656</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>297402246238.495</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>340417169156.038</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>326573601152.15</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>266809915116.952</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>202103060355.51</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-12710690574.0501</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-7061149798.5222</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-2764299054.62769</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>280270065.038449</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>4373241670.63568</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-1340381620.59387</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>684634657.148186</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1944899948.46731</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-14823982722.7526</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-807608953.169737</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-6872692051.6034</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-8574276273.6241</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>5096892091.73238</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-14026563037.654</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-43778264957.8751</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>167903912812.512</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>153341219861.723</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>124075984672.709</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>146101586319.63</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>193515554887.595</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>208843843270.948</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>202769203796.631</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>197807743839.946</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>282544024426.072</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>260478851513.825</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>304274938290.099</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>348991445429.663</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>321476709060.417</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>280836478154.606</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>245881325313.385</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>3959023.33234813</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>3335024.58012089</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>2972834.8451858</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>3265300.1765467</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>3563989.25947044</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>3618915.49231632</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>3775998.54449803</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>4005612.83717569</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>4729267.65200702</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>4313314.06240661</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>4035585.71084973</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>3506119.93116708</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>2905200.86237481</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>2498950.35718085</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>2314961.78344353</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3971149.33490217</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3478094.70577808</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3254982.423727</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3658708.92544928</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>3951972.09054998</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>4189608.37876874</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>4524813.76665638</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>4735810.60022063</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>5483687.64711417</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>5231180.63988637</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>4902086.26942063</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>4384066.44346848</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>3738573.87269945</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>3121430.31269655</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>2934237.30827123</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>318.93</t>
+          <t>19400.2653979951</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>308.39</t>
+          <t>20026.5093451831</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>299.81</t>
+          <t>19441.5960316124</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>267.86</t>
+          <t>21316.9265954174</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>254.86</t>
+          <t>24659.1849342675</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>222.45</t>
+          <t>26084.0796568998</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>212.26</t>
+          <t>25486.7302695167</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>216.39</t>
+          <t>27497.3977791202</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>262.93</t>
+          <t>33907.5962817625</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>227.17</t>
+          <t>44264.0511210012</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>234.88</t>
+          <t>49829.5222957904</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>222.92</t>
+          <t>62804.6600511222</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>220.36</t>
+          <t>79138.4897720259</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>211.26</t>
+          <t>90745.1919103551</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>205.95</t>
+          <t>79203.1585950336</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>330.6</t>
+          <t>312352865974.327</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>317.61</t>
+          <t>255081972049.494</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>308.66</t>
+          <t>249368799106.423</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>315.65</t>
+          <t>291704264091.784</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>338.97</t>
+          <t>306209657494.184</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>337.55</t>
+          <t>324115784827.76</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>325.04</t>
+          <t>358969034036.967</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>332.16</t>
+          <t>386895670891.363</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>369.54</t>
+          <t>450330370522.5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>342.85</t>
+          <t>456578185827.246</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>349.57</t>
+          <t>397309526667.812</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>338.34</t>
+          <t>375545016413.483</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>331.21</t>
+          <t>320743512795.633</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>323.1</t>
+          <t>279244643431.967</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>329.83</t>
+          <t>253647290383.152</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>384.76</t>
+          <t>15701.5489541513</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>369.94</t>
+          <t>16564.0745796391</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>360.29</t>
+          <t>16946.4131944025</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>382.69</t>
+          <t>18844.8451217108</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>427.8</t>
+          <t>21572.0694906245</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>449.38</t>
+          <t>22860.8452831074</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>436.02</t>
+          <t>22774.639078778</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>440.74</t>
+          <t>24223.1221259071</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>325.5</t>
+          <t>28878.827953222</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>437.31</t>
+          <t>38409.2714374573</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>438.09</t>
+          <t>42511.9489207111</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>419.49</t>
+          <t>51665.7075101108</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>413.58</t>
+          <t>64671.5040322085</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>407.14</t>
+          <t>74058.0755815857</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>431.5</t>
+          <t>63756.8959129889</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>855782.682</t>
+          <t>332554241242.306</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>769702.358</t>
+          <t>288677814214.549</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>741810.494</t>
+          <t>287501971248.914</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>871138.595</t>
+          <t>345379838330.209</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>987993.023</t>
+          <t>379449387954.004</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1104799.729</t>
+          <t>384950990421.478</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1258350.709</t>
+          <t>429713419994.315</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1361545.548</t>
+          <t>432183599549.133</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1605075.374</t>
+          <t>494589191213.555</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1565692.366</t>
+          <t>502845594242.399</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1510332.78</t>
+          <t>457594509159.096</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1398078.789</t>
+          <t>408237360280.437</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1244945.1</t>
+          <t>353050001444.223</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1157045.808</t>
+          <t>295170788295.386</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1114800.04</t>
+          <t>227241146916.145</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>783363.66</t>
+          <t>3698.7164438438</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>678243.173</t>
+          <t>3462.43476554404</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>622431.419</t>
+          <t>2495.18283720995</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>716010.466</t>
+          <t>2472.08147370658</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>824291.04</t>
+          <t>3087.11544364306</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>884424.232</t>
+          <t>3223.23437379236</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>977216.129</t>
+          <t>2712.09119073874</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1072703.118</t>
+          <t>3274.27565321305</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1290617.142</t>
+          <t>5028.76832854052</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1204708.618</t>
+          <t>5854.77968354386</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1163055.802</t>
+          <t>7317.57337507933</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1049031.083</t>
+          <t>11138.9525410114</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>910199.43</t>
+          <t>14466.9857398175</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>821654.877</t>
+          <t>16687.1163287694</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>768335.816</t>
+          <t>15446.2626820447</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>625164.587</t>
+          <t>-20201375267.9799</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>541635.013</t>
+          <t>-33595842165.0552</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>515117.229</t>
+          <t>-38133172142.4914</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>598390.188</t>
+          <t>-53675574238.4243</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>639556.655</t>
+          <t>-73239730459.8195</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>691501.993</t>
+          <t>-60835205593.7174</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>772715.12</t>
+          <t>-70744385957.3485</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>819927.97</t>
+          <t>-45287928657.7699</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1003731.569</t>
+          <t>-44258820691.0549</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>997169.267</t>
+          <t>-46267408415.1535</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>936397.319</t>
+          <t>-60284982491.2848</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>850446.512</t>
+          <t>-32692343866.9536</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>738775.838</t>
+          <t>-32306488648.5904</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>653583.706</t>
+          <t>-15926144863.4191</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>601710.227</t>
+          <t>26406143467.0071</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>6543.41082</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>6330.22115</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>5854.3802</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>6099.46493</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>6183.6647</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>5735.96917</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>6003.61016</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>6711.77649</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>8464.65608</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>9868.107</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>10288.20924</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>10976.83176</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>13337.36511</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>14196.60338</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>12450.68179</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>383464.923</t>
+          <t>0.0548782722540715</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>336985.91</t>
+          <t>0.0551880327512054</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>318329.116</t>
+          <t>0.0445906287009296</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>365750.483</t>
+          <t>0.0483580381645788</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>401729.075</t>
+          <t>0.0605726996973952</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>439719.234</t>
+          <t>0.0641955413602526</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>491885.488</t>
+          <t>0.0491647827925677</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>536834.49</t>
+          <t>0.0538649795879701</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>652996.256</t>
+          <t>0.0705633395940494</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>637222.246</t>
+          <t>0.0689547646175802</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>607279.397</t>
+          <t>0.0755258280153297</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>554448.698</t>
+          <t>0.101855351008044</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>480512.818</t>
+          <t>0.113056876418437</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>433850.737</t>
+          <t>0.0967459729953211</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>430363.414</t>
+          <t>0.0777485062500933</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9740.1412712637</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9686.90523316738</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>8888.96000180688</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>9260.24573072016</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9707.83884539053</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>9383.86853228874</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9974.92436313154</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>11218.0306068978</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>13832.6523549874</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>16090.9651895715</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>17349.0987159548</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>18656.0812384003</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>22113.8396061466</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>27381.5534351554</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>26920.620660565</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>174761.309</t>
+          <t>10503.4413717034</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>155936.509</t>
+          <t>10427.3689584264</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>146894.152</t>
+          <t>9558.49779111572</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>169893.431</t>
+          <t>9951.80022776958</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>189617.304</t>
+          <t>10378.5343859256</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>207516.034</t>
+          <t>10026.3418543322</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>235630.519</t>
+          <t>10624.698944257</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>255033.159</t>
+          <t>11924.556829957</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>298474.155</t>
+          <t>14711.22241411</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>286922.779</t>
+          <t>17060.6380435428</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>275137.968</t>
+          <t>18360.608648465</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>253232.523</t>
+          <t>19702.5215524469</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>224712.902</t>
+          <t>23307.9004151758</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>208026.797</t>
+          <t>28874.9325570042</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>198709.347</t>
+          <t>28408.536187663</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>73909.4002712656</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>72364.9433489986</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>65264.9123476706</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>66189.5568281788</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>66293.7003841872</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>60799.2398683111</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>62437.8824717733</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>68342.0313112152</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>84565.0969959058</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>95992.5687797753</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>103732.684074704</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>107404.514445848</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>123173.684150599</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>140071.92969083</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>133436.289238144</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>860.19</t>
+          <t>10503.4413717034</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>769.666</t>
+          <t>10724.2614887281</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>786.368</t>
+          <t>11485.0948823644</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>867.598</t>
+          <t>12182.5752783344</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>941.213</t>
+          <t>12637.43801279</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1066.162</t>
+          <t>13763.6789540906</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1164.667</t>
+          <t>14880.9198597625</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1107.976</t>
+          <t>15483.5148594418</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1079.168</t>
+          <t>15021.8846929607</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>867.55</t>
+          <t>15520.7763738405</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>791.761</t>
+          <t>16020.6517567947</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>651.221</t>
+          <t>15988.5673608761</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>482.007</t>
+          <t>16534.0276955229</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>367.262</t>
+          <t>18421.4570816226</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>423.096</t>
+          <t>19401.1993914635</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>9740.1412712637</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>9950.25374335253</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10706.0225725795</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11360.6098726877</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>11810.336439702</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>12876.4163248351</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>14003.4490929412</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14614.2402729657</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>14167.1980987978</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14693.3330347432</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>15191.3187055785</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>15166.4883979986</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>15741.3070479071</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>17527.2598775341</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>18414.3357135756</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>8231.99386829658</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8256.00944157364</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>7112.09920888428</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>7447.30294223042</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>8621.8011740744</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>8097.73837566782</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7531.80027574296</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8445.74656004296</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>11572.88701589</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>13402.5956564572</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>15321.034761535</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>18673.6362875531</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>23025.4151848242</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>23862.5148029958</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>19623.770802337</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>783363660443.819</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>678243173272.074</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>622431419176.78</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>716010466480.356</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>824291039616.284</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>884424232342.424</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>977216129367.34</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1072703117795.65</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1290617142232.72</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1204708617630.17</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1163055801866.89</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1049031083405.19</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>910199430182.028</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>821654877441.064</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>768335815924.908</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>855782681671.417</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>769702358388.688</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>741810494367.382</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>871138595149.474</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>987993022637.495</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1104799729481.32</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1258350708507.14</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1361545547563.43</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1605075374310.32</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1565692365517.99</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1510332779608.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1398078788822.1</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1244945099608.92</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1157045808302.91</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1114800040208.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>383464923088.08</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>336985910364.396</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>318329115861.928</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>365750483171.323</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>401729075237.239</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>439719233781.783</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>491885488440.516</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>536834489588.479</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>652996255872.109</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>637222246077.675</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>607279396625.884</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>554448697731.122</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>480512817782.686</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>433850737380.009</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>430363413728.034</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>215500</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>221300</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>227900</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>238100</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>250000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>263700</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>278100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>287500</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>292700</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>299300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>308100</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>318900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>333000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>370678.084209208</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>379928.384478628</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>197867.906976744</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>203369.76744186</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>209373.023255814</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>219278.604651163</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>231283.255813953</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>244389.302325581</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>258796.744186047</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>267800</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>272900</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>279300</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>288200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>299200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>313300</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>328800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>331900</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>347656915.269726</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>356524995.788177</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>369457631.879648</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>384402303.337503</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>405671073.680577</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>430517951.58852</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>450568815.623625</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>464122820.701766</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>472770403.81916</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>488325290.497368</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>502605032.235121</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>520128357.329005</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>542962614.873351</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>608295667.828685</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>598728643.090978</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>314909260.115843</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>322522139.691882</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>334261571.025526</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>348888110.389039</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>370291801.692321</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>393849815.76532</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>414010620.901615</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>426888453.077314</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>435428796.830708</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>451041569.253607</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>465532524.894422</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>483123791.169618</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>505824273.094494</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>530592586.963389</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>535239727.255658</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.215648484415565</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.199784726402223</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.194140374058004</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.207255524009581</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.219736006353015</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.239224936158196</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.24046809022498</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.239416943370824</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.146919122300035</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.295206030427211</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.313319246614321</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.281567115377296</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.309432957137098</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.300690257049695</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.379798213490054</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.328135758070723</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.340693467003098</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.389295235470385</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.434256474850671</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.475170925537629</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.463349475360647</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.455797139460949</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.455185052679172</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.432520831947049</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.424571573023134</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.417254082267022</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.435439149657932</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.410471791914278</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.420186507374171</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.41861620311448</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.456215757513712</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.459521806594679</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.416564390471611</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.358488001139748</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.305093068109356</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.297425588481156</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.303734770314071</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.305398003950004</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.420560045752916</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.280222396549656</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.269426671118657</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.282993734964772</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.280095250948624</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.279123235576134</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.201585583395466</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.187988986031401</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.174369102208575</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.170358249670412</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.166459898907562</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.162894742779448</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.162231261084635</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.161585271617819</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.162442826252358</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.117287519285537</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.204285184323656</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.219649700320424</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.193609835066314</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.212430474142803</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.207397959744257</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.269903493699397</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.32007427466936</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.331826193733228</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.38100036497172</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.430793214006936</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.478430059071846</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.47083555952887</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.463212186570251</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.46227552482524</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.475962323149365</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.448918047467116</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.444550979740482</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.460759138469995</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.442084856965206</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.449172959403727</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.467396265874686</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.49193673929924</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.493804704058197</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.448641385357869</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.402746887085502</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.358675198148706</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.366933179386495</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.37520254181193</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.375281648922402</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.406750157565099</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.346796768209227</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.335799319939094</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.345631026463691</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.345484668891991</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.343429080852016</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.262700240425917</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>38211.88115</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>39723.50636</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>37781.09976</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>41560.59266</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>46884.64553</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>48649.6138</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>48930.65896</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>52493.94368</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>65341.3915</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>82023.75847</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>93916.11395</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>113315.88882</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>141769.04186</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>159357.5097</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>140559.4319</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>18735.43524</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>18683.3784</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16670.597</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>17399.10317</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>19000.33556</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18124.08023</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18156.49922</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20370.30339</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>26284.10943</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>30463.2337</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>33681.64341</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>38376.15784</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>46333.3156</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>52737.44736</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>48032.30699</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>53950.0457319127</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>55047.3358078351</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>56404.9582185419</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>57855.4357510982</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>60009.788633893</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>61759.8030138856</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>63738.4676031019</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>65827.6917043733</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>68074.630844625</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>70460.9494699818</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>72747.8329470255</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>75066.6628894579</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>78283.2154087653</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>81384.1564773894</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>83091.2029537598</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
